--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.23518399760718</v>
+        <v>5.563217399611167</v>
       </c>
       <c r="D2" t="n">
-        <v>33.21805613928019</v>
+        <v>5.39793412263303</v>
       </c>
       <c r="E2" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F2" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.89393306835456</v>
+        <v>7.620264123607615</v>
       </c>
       <c r="D3" t="n">
-        <v>45.12620784630366</v>
+        <v>7.333008775024345</v>
       </c>
       <c r="E3" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F3" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.16424849412089</v>
+        <v>6.201690380294645</v>
       </c>
       <c r="D4" t="n">
-        <v>36.40840004726106</v>
+        <v>5.916365007679922</v>
       </c>
       <c r="E4" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F4" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>10.94036168237522</v>
+        <v>1.777808773385974</v>
       </c>
       <c r="D5" t="n">
-        <v>9.734049018046425</v>
+        <v>1.581782965432544</v>
       </c>
       <c r="E5" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F5" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12.81958268538552</v>
+        <v>2.083182186375148</v>
       </c>
       <c r="D6" t="n">
-        <v>13.85523665877568</v>
+        <v>2.251475957051049</v>
       </c>
       <c r="E6" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F6" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.6658315240027</v>
+        <v>5.145697622650439</v>
       </c>
       <c r="D7" t="n">
-        <v>29.89870596513227</v>
+        <v>4.858539719333995</v>
       </c>
       <c r="E7" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F7" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.68996725824604</v>
+        <v>2.062119679464982</v>
       </c>
       <c r="D8" t="n">
-        <v>10.90516642753996</v>
+        <v>1.772089544475243</v>
       </c>
       <c r="E8" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F8" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.60668860002319</v>
+        <v>4.648586897503769</v>
       </c>
       <c r="D9" t="n">
-        <v>30.311866163393</v>
+        <v>4.925678251551362</v>
       </c>
       <c r="E9" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F9" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>51.70692232963619</v>
+        <v>8.40237487856588</v>
       </c>
       <c r="D10" t="n">
-        <v>53.45700428932602</v>
+        <v>8.686763197015479</v>
       </c>
       <c r="E10" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F10" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>19.73072250383174</v>
+        <v>3.206242406872657</v>
       </c>
       <c r="D11" t="n">
-        <v>21.5205825014456</v>
+        <v>3.497094656484909</v>
       </c>
       <c r="E11" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F11" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>12.82416923909387</v>
+        <v>2.083927501352754</v>
       </c>
       <c r="D12" t="n">
-        <v>14.59501330355138</v>
+        <v>2.371689661827099</v>
       </c>
       <c r="E12" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F12" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>53.89639903780093</v>
+        <v>8.758164843642652</v>
       </c>
       <c r="D13" t="n">
-        <v>55.68199601327743</v>
+        <v>9.048324352157584</v>
       </c>
       <c r="E13" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F13" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>50.51772890773574</v>
+        <v>8.20913094750706</v>
       </c>
       <c r="D14" t="n">
-        <v>52.29425259226235</v>
+        <v>8.497816046242633</v>
       </c>
       <c r="E14" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F14" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>9.527222934209428</v>
+        <v>1.548173726809032</v>
       </c>
       <c r="D15" t="n">
-        <v>10.19108678411218</v>
+        <v>1.65605160241823</v>
       </c>
       <c r="E15" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F15" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>2.186476988018807</v>
+        <v>0.3553025105530561</v>
       </c>
       <c r="D16" t="n">
-        <v>1.682778995520942</v>
+        <v>0.2734515867721531</v>
       </c>
       <c r="E16" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F16" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>24.04493674748421</v>
+        <v>3.907302221466184</v>
       </c>
       <c r="D17" t="n">
-        <v>22.95236655306212</v>
+        <v>3.729759564872595</v>
       </c>
       <c r="E17" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F17" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>46.5498786804253</v>
+        <v>7.564355285569111</v>
       </c>
       <c r="D18" t="n">
-        <v>26.66785796015785</v>
+        <v>4.333526918525651</v>
       </c>
       <c r="E18" t="n">
-        <v>16.56969338750733</v>
+        <v>2.692575175469942</v>
       </c>
       <c r="F18" t="n">
-        <v>16.24459436288706</v>
+        <v>2.639746583969148</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
